--- a/data/trans_bre/IMC_inf_MED_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Habitat-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-7.055996247090773</v>
+        <v>-5.686081719879709</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-7.206695945938324</v>
+        <v>-9.621136211980803</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.357942090085601</v>
+        <v>2.638655290276068</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.2563628823688519</v>
+        <v>-0.2176027122817571</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.2839127443785708</v>
+        <v>-0.3866443574763734</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.08340765514397813</v>
+        <v>0.1757161811138956</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-16.88312393609627</v>
+        <v>-14.57531096254736</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-17.45129679114313</v>
+        <v>-17.53327218081532</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-10.23159833803858</v>
+        <v>-8.435694625467766</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.5181258505226554</v>
+        <v>-0.4759113970894155</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.5713970273850651</v>
+        <v>-0.6088022849892745</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.471324895824643</v>
+        <v>-0.3847697170843826</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3.395508886770124</v>
+        <v>4.28895699862895</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.212508905719353</v>
+        <v>-0.5216563406102074</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12.79110779339032</v>
+        <v>13.3445681567433</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1700882537474822</v>
+        <v>0.207714317698553</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1163589948664861</v>
+        <v>0.006086315131146445</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.16288535762159</v>
+        <v>1.533120226637887</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-9.752466728704576</v>
+        <v>-10.12869564742779</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-10.15587191281598</v>
+        <v>-10.3128382902486</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-17.80754557038776</v>
+        <v>-16.29632325835084</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.3354661778979086</v>
+        <v>-0.3678566100711845</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.5134886550191244</v>
+        <v>-0.5443465965769577</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.6478371167980514</v>
+        <v>-0.6164237390473191</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-17.3831030625553</v>
+        <v>-17.33883672154567</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-16.26988642015085</v>
+        <v>-15.56741363126504</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-27.06228218641745</v>
+        <v>-24.89969044398547</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.5308451911547224</v>
+        <v>-0.5647156413282702</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.6888144419897404</v>
+        <v>-0.7007377164751392</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.8257269858483637</v>
+        <v>-0.8051944944626146</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-1.437106283382922</v>
+        <v>-3.394729636372731</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-3.765826908451671</v>
+        <v>-4.411424544057181</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-7.15301924005491</v>
+        <v>-6.725450225261488</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.05639486713334898</v>
+        <v>-0.1389047051335393</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.2281822057844059</v>
+        <v>-0.2759179974476512</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.2987254079688884</v>
+        <v>-0.2874097537422621</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-5.342953621632423</v>
+        <v>-0.8501744446821391</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-6.354702146484928</v>
+        <v>-5.228861274538802</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-3.174921787777865</v>
+        <v>-2.106567405718208</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.169928586219706</v>
+        <v>-0.03163673078071234</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.2896236266887067</v>
+        <v>-0.2554333377752198</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.2356198267290549</v>
+        <v>-0.1585076131637829</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-14.79499161203971</v>
+        <v>-9.377725117320161</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-14.24161289825033</v>
+        <v>-12.39401566665223</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-13.11881927086959</v>
+        <v>-11.76036750171891</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.4071008055673781</v>
+        <v>-0.297360118499928</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.536236520269905</v>
+        <v>-0.5057366791842917</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.7160823933249719</v>
+        <v>-0.6590140748862935</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3.626907693660243</v>
+        <v>7.912491234327568</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2.008530194030909</v>
+        <v>1.940180872317715</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6.811370729741367</v>
+        <v>7.743897908432096</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1580268277718733</v>
+        <v>0.3635431826770957</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.1236622679608167</v>
+        <v>0.1145899377663521</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.817269197585587</v>
+        <v>1.030512613474369</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-2.991122264885654</v>
+        <v>-1.548256497469882</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-5.840925597090632</v>
+        <v>-4.704617477087111</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-6.712317449368616</v>
+        <v>-6.704494097378828</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1207613688967615</v>
+        <v>-0.06746990765418871</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2876694128728832</v>
+        <v>-0.256720475621883</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3726123149036754</v>
+        <v>-0.3850704814991031</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-11.54893045872867</v>
+        <v>-9.370241546481459</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-13.15179518207331</v>
+        <v>-11.8867565051243</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-17.7821263501707</v>
+        <v>-16.31074294632065</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.4024350787395714</v>
+        <v>-0.3317431871462282</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5477063693835069</v>
+        <v>-0.5458066376971357</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.7225980162504384</v>
+        <v>-0.7051396902651429</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>5.166757688825468</v>
+        <v>6.505224211261315</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1.553830841056525</v>
+        <v>1.091469192871632</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2.889465859416834</v>
+        <v>2.74789040133928</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.2550226556358514</v>
+        <v>0.3298375734433724</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.1106658240412671</v>
+        <v>0.1046181189903484</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.2421763600692955</v>
+        <v>0.3152194577322927</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-6.259348845375815</v>
+        <v>-4.826569291150654</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-7.554169948985562</v>
+        <v>-7.441287865984539</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-8.257425787586413</v>
+        <v>-7.284750954182556</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.2229787193260811</v>
+        <v>-0.1867183351947454</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.3517942825767651</v>
+        <v>-0.3671751801100362</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.4137454233637529</v>
+        <v>-0.3801287632498864</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-10.8824037842611</v>
+        <v>-8.578672224337689</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-11.27018647300211</v>
+        <v>-10.92596402798728</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-13.45718379368242</v>
+        <v>-12.46873446246795</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.3544774762113587</v>
+        <v>-0.3111706882688562</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.4782752908541811</v>
+        <v>-0.4941096014565154</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.5792645635859314</v>
+        <v>-0.5729224617793113</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-1.641347644044664</v>
+        <v>-0.7260693950372041</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-3.917953806249336</v>
+        <v>-3.97515238905609</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-2.891569949231347</v>
+        <v>-2.422193359406978</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.06625092445245986</v>
+        <v>-0.0301810895391834</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-0.1927289360695908</v>
+        <v>-0.2161469352470453</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-0.157786873515665</v>
+        <v>-0.1301259969326855</v>
       </c>
     </row>
     <row r="19">
